--- a/tables/table-8-complete-optimisation-results.xlsx
+++ b/tables/table-8-complete-optimisation-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C15BFC-5373-409B-AFC9-0E790DFAA50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{08C15BFC-5373-409B-AFC9-0E790DFAA50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76E35760-BCC0-4E54-8BB7-38123FFC1430}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FBF3C422-4D26-4871-BBFE-F72D370C3147}"/>
   </bookViews>
@@ -30,46 +30,46 @@
     <t>Architecture</t>
   </si>
   <si>
-    <t>Baseline</t>
-  </si>
-  <si>
-    <t>+ CutMix</t>
-  </si>
-  <si>
-    <t>+ Standard Augmentations</t>
-  </si>
-  <si>
-    <t>+ Targeted Augmentations</t>
-  </si>
-  <si>
-    <t>+ Fine-Tuning</t>
-  </si>
-  <si>
-    <t>Total Improvement</t>
-  </si>
-  <si>
     <t>EfficientNet-B0</t>
   </si>
   <si>
-    <t>+ 1.2%</t>
-  </si>
-  <si>
     <t>MobileNetV2</t>
   </si>
   <si>
     <t>ViT-B/16</t>
   </si>
   <si>
-    <t>+ 2.8%</t>
-  </si>
-  <si>
     <t>CoaT-Lite Medium</t>
   </si>
   <si>
-    <t>+ 2.0%</t>
-  </si>
-  <si>
     <t>Table 8: Complete Optimisation Results</t>
+  </si>
+  <si>
+    <t>Baseline (%)</t>
+  </si>
+  <si>
+    <t>+ CutMix (%)</t>
+  </si>
+  <si>
+    <t>+ Standard Augmentations (%)</t>
+  </si>
+  <si>
+    <t>+ Targeted Augmentations (%)</t>
+  </si>
+  <si>
+    <t>+ Fine-Tuning (%)</t>
+  </si>
+  <si>
+    <t>Total Improvement (%)</t>
+  </si>
+  <si>
+    <t>+ 1.2</t>
+  </si>
+  <si>
+    <t>+ 2.8</t>
+  </si>
+  <si>
+    <t>+ 2.0</t>
   </si>
 </sst>
 </file>
@@ -77,7 +77,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -108,12 +108,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -160,49 +166,49 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -524,136 +530,138 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.98</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.97599999999999998</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.996</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>8</v>
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10">
+        <v>98.4</v>
+      </c>
+      <c r="C3" s="10">
+        <v>98.8</v>
+      </c>
+      <c r="D3" s="10">
+        <v>98</v>
+      </c>
+      <c r="E3" s="10">
+        <v>97.6</v>
+      </c>
+      <c r="F3" s="11">
+        <v>99.6</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0.98</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>8</v>
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12">
+        <v>98.8</v>
+      </c>
+      <c r="C4" s="12">
+        <v>98</v>
+      </c>
+      <c r="D4" s="12">
+        <v>99.2</v>
+      </c>
+      <c r="E4" s="12">
+        <v>98.8</v>
+      </c>
+      <c r="F4" s="13">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="7">
-        <v>0.97199999999999998</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>11</v>
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12">
+        <v>97.2</v>
+      </c>
+      <c r="C5" s="12">
+        <v>99.2</v>
+      </c>
+      <c r="D5" s="12">
+        <v>98.8</v>
+      </c>
+      <c r="E5" s="12">
+        <v>98.4</v>
+      </c>
+      <c r="F5" s="13">
+        <v>100</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="11">
-        <v>0.97599999999999998</v>
-      </c>
-      <c r="C6" s="11">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="D6" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="E6" s="11">
-        <v>0.95199999999999996</v>
-      </c>
-      <c r="F6" s="12">
-        <v>0.996</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>13</v>
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14">
+        <v>97.6</v>
+      </c>
+      <c r="C6" s="14">
+        <v>98.8</v>
+      </c>
+      <c r="D6" s="14">
+        <v>98</v>
+      </c>
+      <c r="E6" s="14">
+        <v>95.2</v>
+      </c>
+      <c r="F6" s="15">
+        <v>99.6</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
